--- a/Assets/Config/Excel/Item.xlsx
+++ b/Assets/Config/Excel/Item.xlsx
@@ -474,7 +474,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>IconPath</t>
+          <t>SpriteId</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>图标(只客户端)</t>
+          <t>图ID(填 UISprite 表的 Id)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
